--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4303"/>
+  <dimension ref="A1:F4304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86472,19 +86472,39 @@
         <v>46276</v>
       </c>
       <c r="B4303" t="n">
-        <v>183.85</v>
+        <v>183.8500061035156</v>
       </c>
       <c r="C4303" t="n">
-        <v>184.96</v>
+        <v>184.9600067138672</v>
       </c>
       <c r="D4303" t="n">
-        <v>183.18</v>
+        <v>183.1799926757812</v>
       </c>
       <c r="E4303" t="n">
-        <v>184.86</v>
+        <v>184.8600006103516</v>
       </c>
       <c r="F4303" t="n">
         <v>5688704</v>
+      </c>
+    </row>
+    <row r="4304">
+      <c r="A4304" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B4304" t="n">
+        <v>182.55</v>
+      </c>
+      <c r="C4304" t="n">
+        <v>183.38</v>
+      </c>
+      <c r="D4304" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="E4304" t="n">
+        <v>181.19</v>
+      </c>
+      <c r="F4304" t="n">
+        <v>5274931</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4304"/>
+  <dimension ref="A1:F4305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86492,19 +86492,39 @@
         <v>46279</v>
       </c>
       <c r="B4304" t="n">
-        <v>182.55</v>
+        <v>182.5500030517578</v>
       </c>
       <c r="C4304" t="n">
-        <v>183.38</v>
+        <v>183.3800048828125</v>
       </c>
       <c r="D4304" t="n">
-        <v>180.8</v>
+        <v>180.8000030517578</v>
       </c>
       <c r="E4304" t="n">
-        <v>181.19</v>
+        <v>181.1900024414062</v>
       </c>
       <c r="F4304" t="n">
         <v>5274931</v>
+      </c>
+    </row>
+    <row r="4305">
+      <c r="A4305" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B4305" t="n">
+        <v>183.89</v>
+      </c>
+      <c r="C4305" t="n">
+        <v>184.78</v>
+      </c>
+      <c r="D4305" t="n">
+        <v>182.08</v>
+      </c>
+      <c r="E4305" t="n">
+        <v>183.21</v>
+      </c>
+      <c r="F4305" t="n">
+        <v>2573462</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4305"/>
+  <dimension ref="A1:F4306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86512,19 +86512,39 @@
         <v>46280</v>
       </c>
       <c r="B4305" t="n">
-        <v>183.89</v>
+        <v>183.8899993896484</v>
       </c>
       <c r="C4305" t="n">
-        <v>184.78</v>
+        <v>184.7799987792969</v>
       </c>
       <c r="D4305" t="n">
-        <v>182.08</v>
+        <v>182.0800018310547</v>
       </c>
       <c r="E4305" t="n">
-        <v>183.21</v>
+        <v>183.2100067138672</v>
       </c>
       <c r="F4305" t="n">
         <v>2573462</v>
+      </c>
+    </row>
+    <row r="4306">
+      <c r="A4306" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B4306" t="n">
+        <v>182.66</v>
+      </c>
+      <c r="C4306" t="n">
+        <v>183.95</v>
+      </c>
+      <c r="D4306" t="n">
+        <v>181.86</v>
+      </c>
+      <c r="E4306" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="F4306" t="n">
+        <v>5075730</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4306"/>
+  <dimension ref="A1:F4307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86532,19 +86532,39 @@
         <v>46281</v>
       </c>
       <c r="B4306" t="n">
-        <v>182.66</v>
+        <v>182.6600036621094</v>
       </c>
       <c r="C4306" t="n">
-        <v>183.95</v>
+        <v>183.9499969482422</v>
       </c>
       <c r="D4306" t="n">
-        <v>181.86</v>
+        <v>181.8600006103516</v>
       </c>
       <c r="E4306" t="n">
         <v>183.5</v>
       </c>
       <c r="F4306" t="n">
         <v>5075730</v>
+      </c>
+    </row>
+    <row r="4307">
+      <c r="A4307" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B4307" t="n">
+        <v>183.28</v>
+      </c>
+      <c r="C4307" t="n">
+        <v>184.06</v>
+      </c>
+      <c r="D4307" t="n">
+        <v>180.08</v>
+      </c>
+      <c r="E4307" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="F4307" t="n">
+        <v>2564638</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4307"/>
+  <dimension ref="A1:F4308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86551,20 +86551,32 @@
       <c r="A4307" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B4307" t="n">
-        <v>183.28</v>
-      </c>
-      <c r="C4307" t="n">
-        <v>184.06</v>
-      </c>
-      <c r="D4307" t="n">
-        <v>180.08</v>
-      </c>
-      <c r="E4307" t="n">
-        <v>183.25</v>
-      </c>
+      <c r="B4307" t="inlineStr"/>
+      <c r="C4307" t="inlineStr"/>
+      <c r="D4307" t="inlineStr"/>
+      <c r="E4307" t="inlineStr"/>
       <c r="F4307" t="n">
-        <v>2564638</v>
+        <v>5694501</v>
+      </c>
+    </row>
+    <row r="4308">
+      <c r="A4308" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B4308" t="n">
+        <v>182.47</v>
+      </c>
+      <c r="C4308" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="D4308" t="n">
+        <v>181.52</v>
+      </c>
+      <c r="E4308" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="F4308" t="n">
+        <v>5714224</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4308"/>
+  <dimension ref="A1:F4309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86551,12 +86551,20 @@
       <c r="A4307" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B4307" t="inlineStr"/>
-      <c r="C4307" t="inlineStr"/>
-      <c r="D4307" t="inlineStr"/>
-      <c r="E4307" t="inlineStr"/>
+      <c r="B4307" t="n">
+        <v>183.2799987792969</v>
+      </c>
+      <c r="C4307" t="n">
+        <v>184.0599975585938</v>
+      </c>
+      <c r="D4307" t="n">
+        <v>180.0800018310547</v>
+      </c>
+      <c r="E4307" t="n">
+        <v>183.25</v>
+      </c>
       <c r="F4307" t="n">
-        <v>5694501</v>
+        <v>2564638</v>
       </c>
     </row>
     <row r="4308">
@@ -86564,19 +86572,39 @@
         <v>46283</v>
       </c>
       <c r="B4308" t="n">
-        <v>182.47</v>
+        <v>182.4700012207031</v>
       </c>
       <c r="C4308" t="n">
-        <v>182.6</v>
+        <v>182.6000061035156</v>
       </c>
       <c r="D4308" t="n">
-        <v>181.52</v>
+        <v>181.5200042724609</v>
       </c>
       <c r="E4308" t="n">
-        <v>182.6</v>
+        <v>182.6000061035156</v>
       </c>
       <c r="F4308" t="n">
         <v>5714224</v>
+      </c>
+    </row>
+    <row r="4309">
+      <c r="A4309" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B4309" t="n">
+        <v>183.95</v>
+      </c>
+      <c r="C4309" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="D4309" t="n">
+        <v>182.56</v>
+      </c>
+      <c r="E4309" t="n">
+        <v>183.22</v>
+      </c>
+      <c r="F4309" t="n">
+        <v>3391839</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4309"/>
+  <dimension ref="A1:F4310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86592,19 +86592,39 @@
         <v>46286</v>
       </c>
       <c r="B4309" t="n">
-        <v>183.95</v>
+        <v>183.9499969482422</v>
       </c>
       <c r="C4309" t="n">
-        <v>184.6</v>
+        <v>184.6000061035156</v>
       </c>
       <c r="D4309" t="n">
-        <v>182.56</v>
+        <v>182.5599975585938</v>
       </c>
       <c r="E4309" t="n">
-        <v>183.22</v>
+        <v>183.2200012207031</v>
       </c>
       <c r="F4309" t="n">
         <v>3391839</v>
+      </c>
+    </row>
+    <row r="4310">
+      <c r="A4310" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4310" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="C4310" t="n">
+        <v>184.86</v>
+      </c>
+      <c r="D4310" t="n">
+        <v>181.96</v>
+      </c>
+      <c r="E4310" t="n">
+        <v>182.46</v>
+      </c>
+      <c r="F4310" t="n">
+        <v>2603732</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4310"/>
+  <dimension ref="A1:F4311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86612,19 +86612,39 @@
         <v>46287</v>
       </c>
       <c r="B4310" t="n">
-        <v>184.3</v>
+        <v>184.3000030517578</v>
       </c>
       <c r="C4310" t="n">
-        <v>184.86</v>
+        <v>184.8600006103516</v>
       </c>
       <c r="D4310" t="n">
-        <v>181.96</v>
+        <v>181.9600067138672</v>
       </c>
       <c r="E4310" t="n">
-        <v>182.46</v>
+        <v>182.4600067138672</v>
       </c>
       <c r="F4310" t="n">
         <v>2603732</v>
+      </c>
+    </row>
+    <row r="4311">
+      <c r="A4311" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B4311" t="n">
+        <v>182.86</v>
+      </c>
+      <c r="C4311" t="n">
+        <v>185.9</v>
+      </c>
+      <c r="D4311" t="n">
+        <v>182.71</v>
+      </c>
+      <c r="E4311" t="n">
+        <v>183.06</v>
+      </c>
+      <c r="F4311" t="n">
+        <v>3053965</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4311"/>
+  <dimension ref="A1:F4312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86632,19 +86632,39 @@
         <v>46288</v>
       </c>
       <c r="B4311" t="n">
-        <v>182.86</v>
+        <v>182.8600006103516</v>
       </c>
       <c r="C4311" t="n">
-        <v>185.9</v>
+        <v>185.8999938964844</v>
       </c>
       <c r="D4311" t="n">
-        <v>182.71</v>
+        <v>182.7100067138672</v>
       </c>
       <c r="E4311" t="n">
-        <v>183.06</v>
+        <v>183.0599975585938</v>
       </c>
       <c r="F4311" t="n">
         <v>3053965</v>
+      </c>
+    </row>
+    <row r="4312">
+      <c r="A4312" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B4312" t="n">
+        <v>180.87</v>
+      </c>
+      <c r="C4312" t="n">
+        <v>183.39</v>
+      </c>
+      <c r="D4312" t="n">
+        <v>180.87</v>
+      </c>
+      <c r="E4312" t="n">
+        <v>182.79</v>
+      </c>
+      <c r="F4312" t="n">
+        <v>3542200</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4312"/>
+  <dimension ref="A1:F4313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86652,19 +86652,39 @@
         <v>46289</v>
       </c>
       <c r="B4312" t="n">
-        <v>180.87</v>
+        <v>180.8699951171875</v>
       </c>
       <c r="C4312" t="n">
-        <v>183.39</v>
+        <v>183.3899993896484</v>
       </c>
       <c r="D4312" t="n">
-        <v>180.87</v>
+        <v>180.8699951171875</v>
       </c>
       <c r="E4312" t="n">
-        <v>182.79</v>
+        <v>182.7899932861328</v>
       </c>
       <c r="F4312" t="n">
         <v>3542200</v>
+      </c>
+    </row>
+    <row r="4313">
+      <c r="A4313" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B4313" t="n">
+        <v>180.82</v>
+      </c>
+      <c r="C4313" t="n">
+        <v>181.44</v>
+      </c>
+      <c r="D4313" t="n">
+        <v>179.27</v>
+      </c>
+      <c r="E4313" t="n">
+        <v>180.87</v>
+      </c>
+      <c r="F4313" t="n">
+        <v>4333605</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4313"/>
+  <dimension ref="A1:F4314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86672,19 +86672,39 @@
         <v>46290</v>
       </c>
       <c r="B4313" t="n">
-        <v>180.82</v>
+        <v>180.8200073242188</v>
       </c>
       <c r="C4313" t="n">
-        <v>181.44</v>
+        <v>181.4400024414062</v>
       </c>
       <c r="D4313" t="n">
-        <v>179.27</v>
+        <v>179.2700042724609</v>
       </c>
       <c r="E4313" t="n">
-        <v>180.87</v>
+        <v>180.8699951171875</v>
       </c>
       <c r="F4313" t="n">
         <v>4333605</v>
+      </c>
+    </row>
+    <row r="4314">
+      <c r="A4314" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B4314" t="n">
+        <v>180.18</v>
+      </c>
+      <c r="C4314" t="n">
+        <v>181.36</v>
+      </c>
+      <c r="D4314" t="n">
+        <v>179.03</v>
+      </c>
+      <c r="E4314" t="n">
+        <v>179.78</v>
+      </c>
+      <c r="F4314" t="n">
+        <v>2348492</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4314"/>
+  <dimension ref="A1:F4315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86692,19 +86692,39 @@
         <v>46293</v>
       </c>
       <c r="B4314" t="n">
-        <v>180.18</v>
+        <v>180.1799926757812</v>
       </c>
       <c r="C4314" t="n">
-        <v>181.36</v>
+        <v>181.3600006103516</v>
       </c>
       <c r="D4314" t="n">
-        <v>179.03</v>
+        <v>179.0299987792969</v>
       </c>
       <c r="E4314" t="n">
-        <v>179.78</v>
+        <v>179.7799987792969</v>
       </c>
       <c r="F4314" t="n">
         <v>2348492</v>
+      </c>
+    </row>
+    <row r="4315">
+      <c r="A4315" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B4315" t="n">
+        <v>181.05</v>
+      </c>
+      <c r="C4315" t="n">
+        <v>181.05</v>
+      </c>
+      <c r="D4315" t="n">
+        <v>178.68</v>
+      </c>
+      <c r="E4315" t="n">
+        <v>179.31</v>
+      </c>
+      <c r="F4315" t="n">
+        <v>3269270</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4315"/>
+  <dimension ref="A1:F4316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86712,19 +86712,39 @@
         <v>46294</v>
       </c>
       <c r="B4315" t="n">
-        <v>181.05</v>
+        <v>181.0500030517578</v>
       </c>
       <c r="C4315" t="n">
-        <v>181.05</v>
+        <v>181.0500030517578</v>
       </c>
       <c r="D4315" t="n">
-        <v>178.68</v>
+        <v>178.6799926757812</v>
       </c>
       <c r="E4315" t="n">
-        <v>179.31</v>
+        <v>179.3099975585938</v>
       </c>
       <c r="F4315" t="n">
         <v>3269270</v>
+      </c>
+    </row>
+    <row r="4316">
+      <c r="A4316" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B4316" t="n">
+        <v>184.08</v>
+      </c>
+      <c r="C4316" t="n">
+        <v>185.04</v>
+      </c>
+      <c r="D4316" t="n">
+        <v>181.89</v>
+      </c>
+      <c r="E4316" t="n">
+        <v>183.99</v>
+      </c>
+      <c r="F4316" t="n">
+        <v>3631178</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4316"/>
+  <dimension ref="A1:F4317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86732,19 +86732,39 @@
         <v>46295</v>
       </c>
       <c r="B4316" t="n">
-        <v>184.08</v>
+        <v>184.0800018310547</v>
       </c>
       <c r="C4316" t="n">
-        <v>185.04</v>
+        <v>185.0399932861328</v>
       </c>
       <c r="D4316" t="n">
-        <v>181.89</v>
+        <v>181.8899993896484</v>
       </c>
       <c r="E4316" t="n">
-        <v>183.99</v>
+        <v>183.9900054931641</v>
       </c>
       <c r="F4316" t="n">
         <v>3631178</v>
+      </c>
+    </row>
+    <row r="4317">
+      <c r="A4317" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B4317" t="n">
+        <v>184.41</v>
+      </c>
+      <c r="C4317" t="n">
+        <v>184.66</v>
+      </c>
+      <c r="D4317" t="n">
+        <v>181.88</v>
+      </c>
+      <c r="E4317" t="n">
+        <v>183.69</v>
+      </c>
+      <c r="F4317" t="n">
+        <v>3141960</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4317"/>
+  <dimension ref="A1:F4318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86752,19 +86752,39 @@
         <v>46296</v>
       </c>
       <c r="B4317" t="n">
-        <v>184.41</v>
+        <v>184.4100036621094</v>
       </c>
       <c r="C4317" t="n">
-        <v>184.66</v>
+        <v>185.0399932861328</v>
       </c>
       <c r="D4317" t="n">
-        <v>181.88</v>
+        <v>181.8800048828125</v>
       </c>
       <c r="E4317" t="n">
-        <v>183.69</v>
+        <v>183.9900054931641</v>
       </c>
       <c r="F4317" t="n">
         <v>3141960</v>
+      </c>
+    </row>
+    <row r="4318">
+      <c r="A4318" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B4318" t="n">
+        <v>190</v>
+      </c>
+      <c r="C4318" t="n">
+        <v>190.79</v>
+      </c>
+      <c r="D4318" t="n">
+        <v>183.22</v>
+      </c>
+      <c r="E4318" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="F4318" t="n">
+        <v>6977538</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4318"/>
+  <dimension ref="A1:F4319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86775,16 +86775,36 @@
         <v>190</v>
       </c>
       <c r="C4318" t="n">
-        <v>190.79</v>
+        <v>190</v>
       </c>
       <c r="D4318" t="n">
-        <v>183.22</v>
+        <v>183.2200012207031</v>
       </c>
       <c r="E4318" t="n">
-        <v>187.2</v>
+        <v>187.1999969482422</v>
       </c>
       <c r="F4318" t="n">
         <v>6977538</v>
+      </c>
+    </row>
+    <row r="4319">
+      <c r="A4319" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B4319" t="n">
+        <v>204.35</v>
+      </c>
+      <c r="C4319" t="n">
+        <v>207</v>
+      </c>
+      <c r="D4319" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="E4319" t="n">
+        <v>203.61</v>
+      </c>
+      <c r="F4319" t="n">
+        <v>15307359</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4319"/>
+  <dimension ref="A1:F4320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86204,7 +86204,7 @@
         <v>166.1100006103516</v>
       </c>
       <c r="F4289" t="n">
-        <v>7503932</v>
+        <v>7491177</v>
       </c>
     </row>
     <row r="4290">
@@ -86792,19 +86792,39 @@
         <v>46300</v>
       </c>
       <c r="B4319" t="n">
-        <v>204.35</v>
+        <v>204.3500061035156</v>
       </c>
       <c r="C4319" t="n">
         <v>207</v>
       </c>
       <c r="D4319" t="n">
-        <v>202.5</v>
+        <v>202.5099945068359</v>
       </c>
       <c r="E4319" t="n">
-        <v>203.61</v>
+        <v>203.6100006103516</v>
       </c>
       <c r="F4319" t="n">
         <v>15307359</v>
+      </c>
+    </row>
+    <row r="4320">
+      <c r="A4320" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B4320" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="C4320" t="n">
+        <v>206.44</v>
+      </c>
+      <c r="D4320" t="n">
+        <v>201.42</v>
+      </c>
+      <c r="E4320" t="n">
+        <v>204.87</v>
+      </c>
+      <c r="F4320" t="n">
+        <v>7765006</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4320"/>
+  <dimension ref="A1:F4321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86815,16 +86815,36 @@
         <v>202.5</v>
       </c>
       <c r="C4320" t="n">
-        <v>206.44</v>
+        <v>206.4400024414062</v>
       </c>
       <c r="D4320" t="n">
-        <v>201.42</v>
+        <v>201.4199981689453</v>
       </c>
       <c r="E4320" t="n">
-        <v>204.87</v>
+        <v>204.8699951171875</v>
       </c>
       <c r="F4320" t="n">
         <v>7765006</v>
+      </c>
+    </row>
+    <row r="4321">
+      <c r="A4321" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B4321" t="n">
+        <v>201.25</v>
+      </c>
+      <c r="C4321" t="n">
+        <v>203.76</v>
+      </c>
+      <c r="D4321" t="n">
+        <v>200.95</v>
+      </c>
+      <c r="E4321" t="n">
+        <v>202.64</v>
+      </c>
+      <c r="F4321" t="n">
+        <v>4587926</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4321"/>
+  <dimension ref="A1:F4322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86835,16 +86835,36 @@
         <v>201.25</v>
       </c>
       <c r="C4321" t="n">
-        <v>203.76</v>
+        <v>203.7599945068359</v>
       </c>
       <c r="D4321" t="n">
-        <v>200.95</v>
+        <v>200.9499969482422</v>
       </c>
       <c r="E4321" t="n">
-        <v>202.64</v>
+        <v>202.6399993896484</v>
       </c>
       <c r="F4321" t="n">
         <v>4587926</v>
+      </c>
+    </row>
+    <row r="4322">
+      <c r="A4322" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B4322" t="n">
+        <v>203.08</v>
+      </c>
+      <c r="C4322" t="n">
+        <v>204.88</v>
+      </c>
+      <c r="D4322" t="n">
+        <v>200.89</v>
+      </c>
+      <c r="E4322" t="n">
+        <v>201.55</v>
+      </c>
+      <c r="F4322" t="n">
+        <v>6520954</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4322"/>
+  <dimension ref="A1:F4323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86852,19 +86852,39 @@
         <v>46303</v>
       </c>
       <c r="B4322" t="n">
-        <v>203.08</v>
+        <v>203.0800018310547</v>
       </c>
       <c r="C4322" t="n">
-        <v>204.88</v>
+        <v>204.8800048828125</v>
       </c>
       <c r="D4322" t="n">
-        <v>200.89</v>
+        <v>200.8899993896484</v>
       </c>
       <c r="E4322" t="n">
-        <v>201.55</v>
+        <v>201.5500030517578</v>
       </c>
       <c r="F4322" t="n">
         <v>6520954</v>
+      </c>
+    </row>
+    <row r="4323">
+      <c r="A4323" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B4323" t="n">
+        <v>205.55</v>
+      </c>
+      <c r="C4323" t="n">
+        <v>206.48</v>
+      </c>
+      <c r="D4323" t="n">
+        <v>204.15</v>
+      </c>
+      <c r="E4323" t="n">
+        <v>204.75</v>
+      </c>
+      <c r="F4323" t="n">
+        <v>7448195</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -86872,13 +86872,13 @@
         <v>46304</v>
       </c>
       <c r="B4323" t="n">
-        <v>205.55</v>
+        <v>205.5500030517578</v>
       </c>
       <c r="C4323" t="n">
-        <v>206.48</v>
+        <v>206.4799957275391</v>
       </c>
       <c r="D4323" t="n">
-        <v>204.15</v>
+        <v>204.1499938964844</v>
       </c>
       <c r="E4323" t="n">
         <v>204.75</v>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4323"/>
+  <dimension ref="A1:F4324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86887,6 +86887,26 @@
         <v>7448195</v>
       </c>
     </row>
+    <row r="4324">
+      <c r="A4324" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4324" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="C4324" t="n">
+        <v>204.84</v>
+      </c>
+      <c r="D4324" t="n">
+        <v>202.85</v>
+      </c>
+      <c r="E4324" t="n">
+        <v>203.98</v>
+      </c>
+      <c r="F4324" t="n">
+        <v>4647264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4324"/>
+  <dimension ref="A1:F4325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86892,19 +86892,39 @@
         <v>46308</v>
       </c>
       <c r="B4324" t="n">
-        <v>203.6</v>
+        <v>203.6000061035156</v>
       </c>
       <c r="C4324" t="n">
-        <v>204.84</v>
+        <v>204.8399963378906</v>
       </c>
       <c r="D4324" t="n">
-        <v>202.85</v>
+        <v>202.8500061035156</v>
       </c>
       <c r="E4324" t="n">
-        <v>203.98</v>
+        <v>203.9799957275391</v>
       </c>
       <c r="F4324" t="n">
         <v>4647264</v>
+      </c>
+    </row>
+    <row r="4325">
+      <c r="A4325" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4325" t="n">
+        <v>203.65</v>
+      </c>
+      <c r="C4325" t="n">
+        <v>204.18</v>
+      </c>
+      <c r="D4325" t="n">
+        <v>200.3</v>
+      </c>
+      <c r="E4325" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="F4325" t="n">
+        <v>8081359</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4325"/>
+  <dimension ref="A1:F4326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86912,19 +86912,39 @@
         <v>46309</v>
       </c>
       <c r="B4325" t="n">
-        <v>203.65</v>
+        <v>203.6499938964844</v>
       </c>
       <c r="C4325" t="n">
-        <v>204.18</v>
+        <v>204.1799926757812</v>
       </c>
       <c r="D4325" t="n">
-        <v>200.3</v>
+        <v>200.3000030517578</v>
       </c>
       <c r="E4325" t="n">
         <v>201.5</v>
       </c>
       <c r="F4325" t="n">
         <v>8081359</v>
+      </c>
+    </row>
+    <row r="4326">
+      <c r="A4326" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4326" t="n">
+        <v>201.39</v>
+      </c>
+      <c r="C4326" t="n">
+        <v>203.38</v>
+      </c>
+      <c r="D4326" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4326" t="n">
+        <v>200.95</v>
+      </c>
+      <c r="F4326" t="n">
+        <v>7759933</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4326"/>
+  <dimension ref="A1:F4327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86932,19 +86932,39 @@
         <v>46310</v>
       </c>
       <c r="B4326" t="n">
-        <v>201.39</v>
+        <v>201.3899993896484</v>
       </c>
       <c r="C4326" t="n">
-        <v>203.38</v>
+        <v>203.3800048828125</v>
       </c>
       <c r="D4326" t="n">
         <v>200</v>
       </c>
       <c r="E4326" t="n">
-        <v>200.95</v>
+        <v>200.9499969482422</v>
       </c>
       <c r="F4326" t="n">
         <v>7759933</v>
+      </c>
+    </row>
+    <row r="4327">
+      <c r="A4327" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4327" t="n">
+        <v>202.3</v>
+      </c>
+      <c r="C4327" t="n">
+        <v>203.19</v>
+      </c>
+      <c r="D4327" t="n">
+        <v>200.17</v>
+      </c>
+      <c r="E4327" t="n">
+        <v>200.22</v>
+      </c>
+      <c r="F4327" t="n">
+        <v>4110315</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4327"/>
+  <dimension ref="A1:F4328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86952,19 +86952,39 @@
         <v>46311</v>
       </c>
       <c r="B4327" t="n">
-        <v>202.3</v>
+        <v>202.3000030517578</v>
       </c>
       <c r="C4327" t="n">
-        <v>203.19</v>
+        <v>203.1900024414062</v>
       </c>
       <c r="D4327" t="n">
-        <v>200.17</v>
+        <v>200.1699981689453</v>
       </c>
       <c r="E4327" t="n">
-        <v>200.22</v>
+        <v>200.2200012207031</v>
       </c>
       <c r="F4327" t="n">
         <v>4110315</v>
+      </c>
+    </row>
+    <row r="4328">
+      <c r="A4328" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4328" t="n">
+        <v>202.42</v>
+      </c>
+      <c r="C4328" t="n">
+        <v>204.24</v>
+      </c>
+      <c r="D4328" t="n">
+        <v>201.02</v>
+      </c>
+      <c r="E4328" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="F4328" t="n">
+        <v>4507525</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4328"/>
+  <dimension ref="A1:F4329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86972,19 +86972,39 @@
         <v>46314</v>
       </c>
       <c r="B4328" t="n">
-        <v>202.42</v>
+        <v>202.4199981689453</v>
       </c>
       <c r="C4328" t="n">
-        <v>204.24</v>
+        <v>204.2400054931641</v>
       </c>
       <c r="D4328" t="n">
-        <v>201.02</v>
+        <v>201.0200042724609</v>
       </c>
       <c r="E4328" t="n">
         <v>203.5</v>
       </c>
       <c r="F4328" t="n">
         <v>4507525</v>
+      </c>
+    </row>
+    <row r="4329">
+      <c r="A4329" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4329" t="n">
+        <v>205.01</v>
+      </c>
+      <c r="C4329" t="n">
+        <v>205.76</v>
+      </c>
+      <c r="D4329" t="n">
+        <v>203.21</v>
+      </c>
+      <c r="E4329" t="n">
+        <v>204.54</v>
+      </c>
+      <c r="F4329" t="n">
+        <v>6119581</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4329"/>
+  <dimension ref="A1:F4330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86992,19 +86992,39 @@
         <v>46315</v>
       </c>
       <c r="B4329" t="n">
-        <v>205.01</v>
+        <v>205.0099945068359</v>
       </c>
       <c r="C4329" t="n">
-        <v>205.76</v>
+        <v>205.7599945068359</v>
       </c>
       <c r="D4329" t="n">
-        <v>203.21</v>
+        <v>203.2100067138672</v>
       </c>
       <c r="E4329" t="n">
-        <v>204.54</v>
+        <v>204.5399932861328</v>
       </c>
       <c r="F4329" t="n">
         <v>6119581</v>
+      </c>
+    </row>
+    <row r="4330">
+      <c r="A4330" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4330" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="C4330" t="n">
+        <v>206.2</v>
+      </c>
+      <c r="D4330" t="n">
+        <v>202.62</v>
+      </c>
+      <c r="E4330" t="n">
+        <v>205.88</v>
+      </c>
+      <c r="F4330" t="n">
+        <v>5452117</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4330"/>
+  <dimension ref="A1:F4331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87015,16 +87015,36 @@
         <v>203.5</v>
       </c>
       <c r="C4330" t="n">
-        <v>206.2</v>
+        <v>206.1999969482422</v>
       </c>
       <c r="D4330" t="n">
-        <v>202.62</v>
+        <v>202.6199951171875</v>
       </c>
       <c r="E4330" t="n">
-        <v>205.88</v>
+        <v>205.8800048828125</v>
       </c>
       <c r="F4330" t="n">
         <v>5452117</v>
+      </c>
+    </row>
+    <row r="4331">
+      <c r="A4331" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4331" t="n">
+        <v>200.96</v>
+      </c>
+      <c r="C4331" t="n">
+        <v>203.07</v>
+      </c>
+      <c r="D4331" t="n">
+        <v>199.89</v>
+      </c>
+      <c r="E4331" t="n">
+        <v>202.29</v>
+      </c>
+      <c r="F4331" t="n">
+        <v>7598772</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4331"/>
+  <dimension ref="A1:F4332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87032,19 +87032,39 @@
         <v>46317</v>
       </c>
       <c r="B4331" t="n">
-        <v>200.96</v>
+        <v>200.9600067138672</v>
       </c>
       <c r="C4331" t="n">
-        <v>203.07</v>
+        <v>203.0700073242188</v>
       </c>
       <c r="D4331" t="n">
-        <v>199.89</v>
+        <v>199.8899993896484</v>
       </c>
       <c r="E4331" t="n">
-        <v>202.29</v>
+        <v>202.2899932861328</v>
       </c>
       <c r="F4331" t="n">
         <v>7598772</v>
+      </c>
+    </row>
+    <row r="4332">
+      <c r="A4332" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4332" t="n">
+        <v>201.69</v>
+      </c>
+      <c r="C4332" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="D4332" t="n">
+        <v>200.23</v>
+      </c>
+      <c r="E4332" t="n">
+        <v>201.13</v>
+      </c>
+      <c r="F4332" t="n">
+        <v>8000330</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4332"/>
+  <dimension ref="A1:F4333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87052,19 +87052,39 @@
         <v>46318</v>
       </c>
       <c r="B4332" t="n">
-        <v>201.69</v>
+        <v>201.6900024414062</v>
       </c>
       <c r="C4332" t="n">
-        <v>202.67</v>
+        <v>202.6699981689453</v>
       </c>
       <c r="D4332" t="n">
-        <v>200.23</v>
+        <v>200.2299957275391</v>
       </c>
       <c r="E4332" t="n">
-        <v>201.13</v>
+        <v>201.1300048828125</v>
       </c>
       <c r="F4332" t="n">
         <v>8000330</v>
+      </c>
+    </row>
+    <row r="4333">
+      <c r="A4333" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4333" t="n">
+        <v>172.42</v>
+      </c>
+      <c r="C4333" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="D4333" t="n">
+        <v>165.06</v>
+      </c>
+      <c r="E4333" t="n">
+        <v>169</v>
+      </c>
+      <c r="F4333" t="n">
+        <v>23702562</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4333"/>
+  <dimension ref="A1:F4334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86204,7 +86204,7 @@
         <v>166.1100006103516</v>
       </c>
       <c r="F4289" t="n">
-        <v>7491177</v>
+        <v>7503932</v>
       </c>
     </row>
     <row r="4290">
@@ -87072,19 +87072,39 @@
         <v>46321</v>
       </c>
       <c r="B4333" t="n">
-        <v>172.42</v>
+        <v>172.4199981689453</v>
       </c>
       <c r="C4333" t="n">
-        <v>176.6</v>
+        <v>175.8200073242188</v>
       </c>
       <c r="D4333" t="n">
-        <v>165.06</v>
+        <v>140</v>
       </c>
       <c r="E4333" t="n">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="F4333" t="n">
-        <v>23702562</v>
+        <v>23799393</v>
+      </c>
+    </row>
+    <row r="4334">
+      <c r="A4334" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4334" t="n">
+        <v>173</v>
+      </c>
+      <c r="C4334" t="n">
+        <v>175.66</v>
+      </c>
+      <c r="D4334" t="n">
+        <v>171.85</v>
+      </c>
+      <c r="E4334" t="n">
+        <v>174.5</v>
+      </c>
+      <c r="F4334" t="n">
+        <v>13360951</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4334"/>
+  <dimension ref="A1:F4335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87095,16 +87095,36 @@
         <v>173</v>
       </c>
       <c r="C4334" t="n">
-        <v>175.66</v>
+        <v>175.6600036621094</v>
       </c>
       <c r="D4334" t="n">
-        <v>171.85</v>
+        <v>171.8999938964844</v>
       </c>
       <c r="E4334" t="n">
         <v>174.5</v>
       </c>
       <c r="F4334" t="n">
         <v>13360951</v>
+      </c>
+    </row>
+    <row r="4335">
+      <c r="A4335" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B4335" t="n">
+        <v>168.47</v>
+      </c>
+      <c r="C4335" t="n">
+        <v>172.11</v>
+      </c>
+      <c r="D4335" t="n">
+        <v>167.16</v>
+      </c>
+      <c r="E4335" t="n">
+        <v>172.11</v>
+      </c>
+      <c r="F4335" t="n">
+        <v>10479741</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4335"/>
+  <dimension ref="A1:F4336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87112,19 +87112,39 @@
         <v>46323</v>
       </c>
       <c r="B4335" t="n">
-        <v>168.47</v>
+        <v>168.4700012207031</v>
       </c>
       <c r="C4335" t="n">
-        <v>172.11</v>
+        <v>172.1100006103516</v>
       </c>
       <c r="D4335" t="n">
-        <v>167.16</v>
+        <v>167.1600036621094</v>
       </c>
       <c r="E4335" t="n">
-        <v>172.11</v>
+        <v>172.1100006103516</v>
       </c>
       <c r="F4335" t="n">
         <v>10479741</v>
+      </c>
+    </row>
+    <row r="4336">
+      <c r="A4336" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B4336" t="n">
+        <v>166.51</v>
+      </c>
+      <c r="C4336" t="n">
+        <v>168.77</v>
+      </c>
+      <c r="D4336" t="n">
+        <v>166</v>
+      </c>
+      <c r="E4336" t="n">
+        <v>168.37</v>
+      </c>
+      <c r="F4336" t="n">
+        <v>5365245</v>
       </c>
     </row>
   </sheetData>

--- a/database/BOVA11.xlsx
+++ b/database/BOVA11.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4336"/>
+  <dimension ref="A1:F4337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87132,19 +87132,39 @@
         <v>46324</v>
       </c>
       <c r="B4336" t="n">
-        <v>166.51</v>
+        <v>166.5099945068359</v>
       </c>
       <c r="C4336" t="n">
-        <v>168.77</v>
+        <v>168.7700042724609</v>
       </c>
       <c r="D4336" t="n">
         <v>166</v>
       </c>
       <c r="E4336" t="n">
-        <v>168.37</v>
+        <v>168.3699951171875</v>
       </c>
       <c r="F4336" t="n">
         <v>5365245</v>
+      </c>
+    </row>
+    <row r="4337">
+      <c r="A4337" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B4337" t="n">
+        <v>165.4</v>
+      </c>
+      <c r="C4337" t="n">
+        <v>166.44</v>
+      </c>
+      <c r="D4337" t="n">
+        <v>164.21</v>
+      </c>
+      <c r="E4337" t="n">
+        <v>164.88</v>
+      </c>
+      <c r="F4337" t="n">
+        <v>9633009</v>
       </c>
     </row>
   </sheetData>
